--- a/docs/content/DigitizWork-Website-Content.xlsx
+++ b/docs/content/DigitizWork-Website-Content.xlsx
@@ -11,15 +11,22 @@
     <sheet name="Site &amp; Contact" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Home page" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="About page" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Consultants" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Images" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Discovery questions" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Change log" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Clients page" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Feedback page" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Clients" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Case studies" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Testimonials" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Consultants" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Images" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Discovery questions" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Change log" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Site &amp; Contact'!$A$1:$K$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Home page'!$A$1:$K$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Site &amp; Contact'!$A$1:$K$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Home page'!$A$1:$K$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'About page'!$A$1:$K$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Clients page'!$A$1:$K$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Feedback page'!$A$1:$K$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -677,7 +684,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Fill in the 'Consultants', 'Discovery questions' and 'Images' tabs where you can.</t>
+          <t>Fill in the 'Consultants', 'Clients', 'Case studies', 'Testimonials', 'Discovery questions' and 'Images' tabs where you can.</t>
         </is>
       </c>
     </row>
@@ -857,6 +864,1137 @@
           <t>Text marked [Placeholder] is temporary. 'Field ID' tells Claude exactly where the text goes on the site, so please don't change it.</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>Show on site? (Yes/No)</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>Job title / role</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Short bio (2-3 sentences)</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Specialisms (comma-separated)</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>LinkedIn URL</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Photo file name</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>Consent to publish (Yes/No)</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>Bio characters</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
+          <t>Notes for Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="n"/>
+      <c r="C2" s="20" t="n"/>
+      <c r="D2" s="20" t="n"/>
+      <c r="E2" s="20" t="n"/>
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="20" t="n"/>
+      <c r="H2" s="20" t="n"/>
+      <c r="I2" s="20" t="n"/>
+      <c r="J2" s="20" t="n"/>
+      <c r="K2" s="21">
+        <f>IF(E2="","",LEN(E2))</f>
+        <v/>
+      </c>
+      <c r="L2" s="20" t="inlineStr">
+        <is>
+          <t>Site currently shows 4 placeholder cards. Add as many people as you need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="20" t="n"/>
+      <c r="E3" s="20" t="n"/>
+      <c r="F3" s="20" t="n"/>
+      <c r="G3" s="20" t="n"/>
+      <c r="H3" s="20" t="n"/>
+      <c r="I3" s="20" t="n"/>
+      <c r="J3" s="20" t="n"/>
+      <c r="K3" s="21">
+        <f>IF(E3="","",LEN(E3))</f>
+        <v/>
+      </c>
+      <c r="L3" s="20" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="20" t="n"/>
+      <c r="C4" s="20" t="n"/>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="20" t="n"/>
+      <c r="F4" s="20" t="n"/>
+      <c r="G4" s="20" t="n"/>
+      <c r="H4" s="20" t="n"/>
+      <c r="I4" s="20" t="n"/>
+      <c r="J4" s="20" t="n"/>
+      <c r="K4" s="21">
+        <f>IF(E4="","",LEN(E4))</f>
+        <v/>
+      </c>
+      <c r="L4" s="20" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="20" t="n"/>
+      <c r="C5" s="20" t="n"/>
+      <c r="D5" s="20" t="n"/>
+      <c r="E5" s="20" t="n"/>
+      <c r="F5" s="20" t="n"/>
+      <c r="G5" s="20" t="n"/>
+      <c r="H5" s="20" t="n"/>
+      <c r="I5" s="20" t="n"/>
+      <c r="J5" s="20" t="n"/>
+      <c r="K5" s="21">
+        <f>IF(E5="","",LEN(E5))</f>
+        <v/>
+      </c>
+      <c r="L5" s="20" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="20" t="n"/>
+      <c r="C6" s="20" t="n"/>
+      <c r="D6" s="20" t="n"/>
+      <c r="E6" s="20" t="n"/>
+      <c r="F6" s="20" t="n"/>
+      <c r="G6" s="20" t="n"/>
+      <c r="H6" s="20" t="n"/>
+      <c r="I6" s="20" t="n"/>
+      <c r="J6" s="20" t="n"/>
+      <c r="K6" s="21">
+        <f>IF(E6="","",LEN(E6))</f>
+        <v/>
+      </c>
+      <c r="L6" s="20" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="20" t="n"/>
+      <c r="C7" s="20" t="n"/>
+      <c r="D7" s="20" t="n"/>
+      <c r="E7" s="20" t="n"/>
+      <c r="F7" s="20" t="n"/>
+      <c r="G7" s="20" t="n"/>
+      <c r="H7" s="20" t="n"/>
+      <c r="I7" s="20" t="n"/>
+      <c r="J7" s="20" t="n"/>
+      <c r="K7" s="21">
+        <f>IF(E7="","",LEN(E7))</f>
+        <v/>
+      </c>
+      <c r="L7" s="20" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="20" t="n"/>
+      <c r="C8" s="20" t="n"/>
+      <c r="D8" s="20" t="n"/>
+      <c r="E8" s="20" t="n"/>
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20" t="n"/>
+      <c r="I8" s="20" t="n"/>
+      <c r="J8" s="20" t="n"/>
+      <c r="K8" s="21">
+        <f>IF(E8="","",LEN(E8))</f>
+        <v/>
+      </c>
+      <c r="L8" s="20" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="20" t="n"/>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="20" t="n"/>
+      <c r="E9" s="20" t="n"/>
+      <c r="F9" s="20" t="n"/>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="20" t="n"/>
+      <c r="I9" s="20" t="n"/>
+      <c r="J9" s="20" t="n"/>
+      <c r="K9" s="21">
+        <f>IF(E9="","",LEN(E9))</f>
+        <v/>
+      </c>
+      <c r="L9" s="20" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Photos:</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Square, at least 800 x 800 px, JPG/PNG/WebP. Send the files with this sheet and put the file name in 'Photo file name'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Consent:</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Each person must agree to their name, bio and photo being published. Cards without 'Yes' are not shown.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2 B3 B4 B5 B6 B7 B8 B9 J2 J3 J4 J5 J6 J7 J8 J9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Image slot</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>Where it appears</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>Current file</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>Description (alt text)</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>New image file name</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Notes for Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>heroAiCore</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>Home - hero</t>
+        </is>
+      </c>
+      <c r="C2" s="22" t="inlineStr">
+        <is>
+          <t>/images/hero/ai-core.svg</t>
+        </is>
+      </c>
+      <c r="D2" s="22" t="inlineStr">
+        <is>
+          <t>Illustration of an AI core connected to a network of nodes, surrounded by panels showing code, a chat conversation and a data chart.</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="n"/>
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="20" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>serviceWebMobile</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>Home - Service 1</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t>/images/services/web-mobile.svg</t>
+        </is>
+      </c>
+      <c r="D3" s="22" t="inlineStr">
+        <is>
+          <t>Illustration of a web browser window and a mobile phone showing an app interface.</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="n"/>
+      <c r="F3" s="20" t="n"/>
+      <c r="G3" s="20" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>serviceAiAssistants</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Home - Service 2</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>/images/services/ai-assistants.svg</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>Illustration of a chat conversation between a person and a glowing AI assistant.</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="n"/>
+      <c r="F4" s="20" t="n"/>
+      <c r="G4" s="20" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>serviceAutomation</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Home - Service 3</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>/images/services/automation.svg</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>Illustration of documents flowing through an AI node and coming out as completed tasks.</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="n"/>
+      <c r="F5" s="20" t="n"/>
+      <c r="G5" s="20" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>serviceDataAnalytics</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Home - Service 4</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>/images/services/data-analytics.svg</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>Illustration of a dashboard with a bar chart, a trend line and a ring chart.</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="n"/>
+      <c r="F6" s="20" t="n"/>
+      <c r="G6" s="20" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>serviceCloudIntegration</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Home - Service 5</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>/images/services/cloud-integration.svg</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>Illustration of a cloud connected to several application blocks.</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="n"/>
+      <c r="F7" s="20" t="n"/>
+      <c r="G7" s="20" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>serviceCustomSoftware</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Home - Service 6</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>/images/services/custom-software.svg</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>Illustration of layered code editor windows with code brackets.</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="n"/>
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="20" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>aboutCollaboration</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Home - About section</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>/images/about/collaboration.svg</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>Illustration of people connected around a central AI node, representing consultants working with AI.</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="n"/>
+      <c r="F9" s="20" t="n"/>
+      <c r="G9" s="20" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>aboutTeamNetwork</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>About page - hero</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>/images/about/team-network.svg</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>Illustration of a network of people linked together around a glowing core.</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="n"/>
+      <c r="F10" s="20" t="n"/>
+      <c r="G10" s="20" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>consultantPlaceholder</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>About page - consultant without photo</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>/images/team/avatar-placeholder.svg</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>(decorative)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="n"/>
+      <c r="F11" s="20" t="n"/>
+      <c r="G11" s="20" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>clientsHero</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Clients page - hero</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>/images/clients/clients-hero.svg</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>Illustration of six abstract organisation tiles connected to a glowing central core.</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>testimonialsHero</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Feedback page - hero</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>/images/testimonials/testimonials-hero.svg</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>Illustration of layered quote cards with abstract text lines and faceless avatars.</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="n"/>
+      <c r="F13" s="20" t="n"/>
+      <c r="G13" s="20" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>clientLogoPlaceholder</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Clients - client without logo</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>/images/clients/logo-placeholder.svg</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>(decorative)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="n"/>
+      <c r="F14" s="20" t="n"/>
+      <c r="G14" s="20" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Note:</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Ready-made AI image prompts and sizes for each slot are in docs/frontend/image-prompts.md. Do not use AI-generated faces for real consultants. Record the licence/terms of any image you supply.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Keep current illustration,Replace with new image"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>What we know so far</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>Your answer</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>What does DigitizWork do? List the services you want on the site (rough bullet points are fine).</t>
+        </is>
+      </c>
+      <c r="C2" s="22" t="inlineStr">
+        <is>
+          <t>Message: 'DigitizWork can deliver any software solution using AI'. Service list on the site is a proposal.</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="n"/>
+      <c r="E2" s="20" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>Who are your customers? Business type and size, industries, B2B or B2C.</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr"/>
+      <c r="D3" s="20" t="n"/>
+      <c r="E3" s="20" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Where do you operate and which markets do you serve? Language and spelling (Australian English?).</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>Based in Melbourne, Australia (confirmed). Markets and spelling not confirmed.</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="20" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Main goal of the site? (enquiries, consultation bookings, recruiting, credibility). Which single action matters most?</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>Assumed: enquiries via the contact form.</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="n"/>
+      <c r="E5" s="20" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Contact details to publish, and which inbox receives form messages?</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>Email consultant@digitizwork.com and Melbourne, Australia (confirmed). Phone, address and form inbox open.</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="n"/>
+      <c r="E6" s="20" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Brand assets: logo, colours, fonts? (send files if you have them)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>None received; the current look is a proposal.</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="n"/>
+      <c r="E7" s="20" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Domain and hosting: do you own a domain? Hosting preference or budget?</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr"/>
+      <c r="D8" s="20" t="n"/>
+      <c r="E8" s="20" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Facts you can confirm: founding year, team size, founder names, legal entity name, ABN.</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr"/>
+      <c r="D9" s="20" t="n"/>
+      <c r="E9" s="20" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Competitor sites or sites you admire (2-5 links), and anything you dislike.</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="20" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Privacy: confirm Australian Privacy Act applies. Cookie consent / analytics needed?</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>Assumed: Australian Privacy Act; no cookies at launch.</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="20" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>Q11</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Analytics: OK to use privacy-friendly cookieless analytics, or none at launch?</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>OQ-3</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Privacy notice: a small /privacy page (recommended) or a section on the page?</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="20" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>OQ-5</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Keep the 'How we work' section? (see Home page tab, approach.enabled)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>Currently shown.</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="20" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>OQ-8</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Does 'launch' mean a local production build only, or a public website after testing?</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="20" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="26" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C1" s="26" t="inlineStr">
+        <is>
+          <t>Changed by</t>
+        </is>
+      </c>
+      <c r="D1" s="26" t="inlineStr">
+        <is>
+          <t>Summary of changes</t>
+        </is>
+      </c>
+      <c r="E1" s="26" t="inlineStr">
+        <is>
+          <t>Jira issue (filled by Claude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="inlineStr">
+        <is>
+          <t>Initial export of current site content (placeholder and draft copy, confirmed email and location).</t>
+        </is>
+      </c>
+      <c r="E2" s="17" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>Added Clients page, Feedback page, home clients teaser, new menu labels, and Clients / Case studies / Testimonials tabs.</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>DIG-59, DIG-60, DIG-61</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="n"/>
+      <c r="B4" s="20" t="n"/>
+      <c r="C4" s="20" t="n"/>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="17" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="n"/>
+      <c r="B5" s="20" t="n"/>
+      <c r="C5" s="20" t="n"/>
+      <c r="D5" s="20" t="n"/>
+      <c r="E5" s="17" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="n"/>
+      <c r="B6" s="20" t="n"/>
+      <c r="C6" s="20" t="n"/>
+      <c r="D6" s="20" t="n"/>
+      <c r="E6" s="17" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="n"/>
+      <c r="B7" s="20" t="n"/>
+      <c r="C7" s="20" t="n"/>
+      <c r="D7" s="20" t="n"/>
+      <c r="E7" s="17" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="n"/>
+      <c r="B8" s="20" t="n"/>
+      <c r="C8" s="20" t="n"/>
+      <c r="D8" s="20" t="n"/>
+      <c r="E8" s="17" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="n"/>
+      <c r="B9" s="20" t="n"/>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="20" t="n"/>
+      <c r="E9" s="17" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="n"/>
+      <c r="B10" s="20" t="n"/>
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="17" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="n"/>
+      <c r="B11" s="20" t="n"/>
+      <c r="C11" s="20" t="n"/>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="17" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="n"/>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="17" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="n"/>
+      <c r="B13" s="20" t="n"/>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -869,7 +2007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1609,7 +2747,7 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>nav.contact</t>
+          <t>nav.clients</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
@@ -1629,7 +2767,7 @@
       </c>
       <c r="E21" s="22" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Clients</t>
         </is>
       </c>
       <c r="F21" s="24" t="inlineStr">
@@ -1651,42 +2789,73 @@
       <c r="K21" s="20" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>FOOTER</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="15" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="15" t="n"/>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
-      <c r="H22" s="15" t="n"/>
-      <c r="I22" s="15" t="n"/>
-      <c r="J22" s="15" t="n"/>
-      <c r="K22" s="15" t="n"/>
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>nav.feedback</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Menu item</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="n"/>
+      <c r="H22" s="20" t="n"/>
+      <c r="I22" s="21">
+        <f>IF(G22="","",LEN(G22))</f>
+        <v/>
+      </c>
+      <c r="J22" s="17" t="inlineStr">
+        <is>
+          <t>1-2 words.</t>
+        </is>
+      </c>
+      <c r="K22" s="20" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>footer.legalLine</t>
+          <t>nav.contact</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Footer</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr"/>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>Menu item</t>
+        </is>
+      </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>Copyright line</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
         <is>
-          <t>DigitizWork. All rights reserved.</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F23" s="24" t="inlineStr">
@@ -1702,7 +2871,7 @@
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>Year is added automatically.</t>
+          <t>1-2 words.</t>
         </is>
       </c>
       <c r="K23" s="20" t="n"/>
@@ -1710,7 +2879,7 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>NEW ITEMS (add rows below if you want extra content)</t>
+          <t>FOOTER</t>
         </is>
       </c>
       <c r="B24" s="15" t="n"/>
@@ -1727,42 +2896,59 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="n"/>
-      <c r="C25" s="20" t="n"/>
-      <c r="D25" s="20" t="n"/>
-      <c r="E25" s="17" t="n"/>
-      <c r="F25" s="17" t="n"/>
+          <t>footer.legalLine</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr"/>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>Copyright line</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>DigitizWork. All rights reserved.</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
       <c r="G25" s="20" t="n"/>
       <c r="H25" s="20" t="n"/>
       <c r="I25" s="21">
         <f>IF(G25="","",LEN(G25))</f>
         <v/>
       </c>
-      <c r="J25" s="20" t="n"/>
+      <c r="J25" s="17" t="inlineStr">
+        <is>
+          <t>Year is added automatically.</t>
+        </is>
+      </c>
       <c r="K25" s="20" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="n"/>
-      <c r="C26" s="20" t="n"/>
-      <c r="D26" s="20" t="n"/>
-      <c r="E26" s="17" t="n"/>
-      <c r="F26" s="17" t="n"/>
-      <c r="G26" s="20" t="n"/>
-      <c r="H26" s="20" t="n"/>
-      <c r="I26" s="21">
-        <f>IF(G26="","",LEN(G26))</f>
-        <v/>
-      </c>
-      <c r="J26" s="20" t="n"/>
-      <c r="K26" s="20" t="n"/>
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>NEW ITEMS (add rows below if you want extra content)</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="15" t="n"/>
+      <c r="H26" s="15" t="n"/>
+      <c r="I26" s="15" t="n"/>
+      <c r="J26" s="15" t="n"/>
+      <c r="K26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
@@ -1824,10 +3010,50 @@
       <c r="J29" s="20" t="n"/>
       <c r="K29" s="20" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="n"/>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="20" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
+      <c r="G30" s="20" t="n"/>
+      <c r="H30" s="20" t="n"/>
+      <c r="I30" s="21">
+        <f>IF(G30="","",LEN(G30))</f>
+        <v/>
+      </c>
+      <c r="J30" s="20" t="n"/>
+      <c r="K30" s="20" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="n"/>
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="17" t="n"/>
+      <c r="G31" s="20" t="n"/>
+      <c r="H31" s="20" t="n"/>
+      <c r="I31" s="21">
+        <f>IF(G31="","",LEN(G31))</f>
+        <v/>
+      </c>
+      <c r="J31" s="20" t="n"/>
+      <c r="K31" s="20" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K29"/>
+  <autoFilter ref="A1:K31"/>
   <dataValidations count="1">
-    <dataValidation sqref="H3 H4 H6 H7 H8 H9 H10 H12 H13 H14 H16 H17 H18 H19 H20 H21 H23 H25 H26 H27 H28 H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H3 H4 H6 H7 H8 H9 H10 H12 H13 H14 H16 H17 H18 H19 H20 H21 H22 H23 H25 H27 H28 H29 H30 H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Keep as is,Replace with new content,Remove,Approve current text"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1841,7 +3067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K89"/>
+  <dimension ref="A1:K96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4646,7 +5872,7 @@
     <row r="69">
       <c r="A69" s="14" t="inlineStr">
         <is>
-          <t>CONTACT</t>
+          <t>CLIENTS TEASER (HOME)</t>
         </is>
       </c>
       <c r="B69" s="15" t="n"/>
@@ -4663,12 +5889,12 @@
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>contact.eyebrow</t>
+          <t>trustedTeaser.eyebrow</t>
         </is>
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Clients teaser (home)</t>
         </is>
       </c>
       <c r="C70" s="17" t="inlineStr"/>
@@ -4679,7 +5905,7 @@
       </c>
       <c r="E70" s="22" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Clients and feedback</t>
         </is>
       </c>
       <c r="F70" s="24" t="inlineStr">
@@ -4695,7 +5921,7 @@
       </c>
       <c r="J70" s="17" t="inlineStr">
         <is>
-          <t>1-2 words.</t>
+          <t>2-4 words.</t>
         </is>
       </c>
       <c r="K70" s="20" t="n"/>
@@ -4703,12 +5929,12 @@
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>contact.title</t>
+          <t>trustedTeaser.title</t>
         </is>
       </c>
       <c r="B71" s="17" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Clients teaser (home)</t>
         </is>
       </c>
       <c r="C71" s="17" t="inlineStr"/>
@@ -4719,7 +5945,7 @@
       </c>
       <c r="E71" s="22" t="inlineStr">
         <is>
-          <t>Let's build something intelligent</t>
+          <t>Trusted by organisations like yours</t>
         </is>
       </c>
       <c r="F71" s="24" t="inlineStr">
@@ -4735,7 +5961,7 @@
       </c>
       <c r="J71" s="17" t="inlineStr">
         <is>
-          <t>Max ~50 characters.</t>
+          <t>Only claim 'trusted by' once real clients are listed.</t>
         </is>
       </c>
       <c r="K71" s="20" t="n"/>
@@ -4743,23 +5969,23 @@
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>contact.intro</t>
+          <t>trustedTeaser.intro</t>
         </is>
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Clients teaser (home)</t>
         </is>
       </c>
       <c r="C72" s="17" t="inlineStr"/>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t>Intro paragraph</t>
+          <t>Intro</t>
         </is>
       </c>
       <c r="E72" s="22" t="inlineStr">
         <is>
-          <t>Tell us about your idea or the problem you want to solve. A consultant will get back to you to talk through the options. [Placeholder: response time to be confirmed]</t>
+          <t>[Placeholder] A short line introducing the organisations DigitizWork works with and what they say.</t>
         </is>
       </c>
       <c r="F72" s="23" t="inlineStr">
@@ -4775,48 +6001,71 @@
       </c>
       <c r="J72" s="17" t="inlineStr">
         <is>
-          <t>Say how fast you reply, e.g. 'within 1 business day'.</t>
+          <t>1 sentence.</t>
         </is>
       </c>
       <c r="K72" s="20" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="14" t="inlineStr">
-        <is>
-          <t>CONTACT FORM</t>
-        </is>
-      </c>
-      <c r="B73" s="15" t="n"/>
-      <c r="C73" s="15" t="n"/>
-      <c r="D73" s="15" t="n"/>
-      <c r="E73" s="15" t="n"/>
-      <c r="F73" s="15" t="n"/>
-      <c r="G73" s="15" t="n"/>
-      <c r="H73" s="15" t="n"/>
-      <c r="I73" s="15" t="n"/>
-      <c r="J73" s="15" t="n"/>
-      <c r="K73" s="15" t="n"/>
+      <c r="A73" s="16" t="inlineStr">
+        <is>
+          <t>trustedTeaser.clientsLabel</t>
+        </is>
+      </c>
+      <c r="B73" s="17" t="inlineStr">
+        <is>
+          <t>Clients teaser (home)</t>
+        </is>
+      </c>
+      <c r="C73" s="17" t="inlineStr"/>
+      <c r="D73" s="17" t="inlineStr">
+        <is>
+          <t>Logo strip label</t>
+        </is>
+      </c>
+      <c r="E73" s="22" t="inlineStr">
+        <is>
+          <t>Some of our clients</t>
+        </is>
+      </c>
+      <c r="F73" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
+      <c r="G73" s="20" t="n"/>
+      <c r="H73" s="20" t="n"/>
+      <c r="I73" s="21">
+        <f>IF(G73="","",LEN(G73))</f>
+        <v/>
+      </c>
+      <c r="J73" s="17" t="inlineStr">
+        <is>
+          <t>2-4 words.</t>
+        </is>
+      </c>
+      <c r="K73" s="20" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="16" t="inlineStr">
         <is>
-          <t>contact.form.title</t>
+          <t>trustedTeaser.clientsLink</t>
         </is>
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>Contact form</t>
+          <t>Clients teaser (home)</t>
         </is>
       </c>
       <c r="C74" s="17" t="inlineStr"/>
       <c r="D74" s="17" t="inlineStr">
         <is>
-          <t>Form heading</t>
+          <t>Link to /clients</t>
         </is>
       </c>
       <c r="E74" s="22" t="inlineStr">
         <is>
-          <t>Send an enquiry</t>
+          <t>See our clients</t>
         </is>
       </c>
       <c r="F74" s="24" t="inlineStr">
@@ -4840,23 +6089,23 @@
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>contact.form.description</t>
+          <t>trustedTeaser.testimonialsLink</t>
         </is>
       </c>
       <c r="B75" s="17" t="inlineStr">
         <is>
-          <t>Contact form</t>
+          <t>Clients teaser (home)</t>
         </is>
       </c>
       <c r="C75" s="17" t="inlineStr"/>
       <c r="D75" s="17" t="inlineStr">
         <is>
-          <t>Form note</t>
+          <t>Link to /testimonials</t>
         </is>
       </c>
       <c r="E75" s="22" t="inlineStr">
         <is>
-          <t>All fields are required unless marked optional.</t>
+          <t>Read client feedback</t>
         </is>
       </c>
       <c r="F75" s="24" t="inlineStr">
@@ -4872,75 +6121,48 @@
       </c>
       <c r="J75" s="17" t="inlineStr">
         <is>
-          <t>1 sentence.</t>
+          <t>2-4 words.</t>
         </is>
       </c>
       <c r="K75" s="20" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="16" t="inlineStr">
-        <is>
-          <t>contact.form.fields.name</t>
-        </is>
-      </c>
-      <c r="B76" s="17" t="inlineStr">
-        <is>
-          <t>Contact form</t>
-        </is>
-      </c>
-      <c r="C76" s="17" t="inlineStr">
-        <is>
-          <t>Field label</t>
-        </is>
-      </c>
-      <c r="D76" s="17" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E76" s="22" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="F76" s="24" t="inlineStr">
-        <is>
-          <t>Draft - needs approval</t>
-        </is>
-      </c>
-      <c r="G76" s="20" t="n"/>
-      <c r="H76" s="20" t="n"/>
-      <c r="I76" s="21">
-        <f>IF(G76="","",LEN(G76))</f>
-        <v/>
-      </c>
-      <c r="J76" s="17" t="inlineStr"/>
-      <c r="K76" s="20" t="n"/>
+      <c r="A76" s="14" t="inlineStr">
+        <is>
+          <t>CONTACT</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="n"/>
+      <c r="C76" s="15" t="n"/>
+      <c r="D76" s="15" t="n"/>
+      <c r="E76" s="15" t="n"/>
+      <c r="F76" s="15" t="n"/>
+      <c r="G76" s="15" t="n"/>
+      <c r="H76" s="15" t="n"/>
+      <c r="I76" s="15" t="n"/>
+      <c r="J76" s="15" t="n"/>
+      <c r="K76" s="15" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
-          <t>contact.form.fields.email</t>
+          <t>contact.eyebrow</t>
         </is>
       </c>
       <c r="B77" s="17" t="inlineStr">
         <is>
-          <t>Contact form</t>
-        </is>
-      </c>
-      <c r="C77" s="17" t="inlineStr">
-        <is>
-          <t>Field label</t>
-        </is>
-      </c>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="C77" s="17" t="inlineStr"/>
       <c r="D77" s="17" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Small label</t>
         </is>
       </c>
       <c r="E77" s="22" t="inlineStr">
         <is>
-          <t>Work email</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F77" s="24" t="inlineStr">
@@ -4954,33 +6176,33 @@
         <f>IF(G77="","",LEN(G77))</f>
         <v/>
       </c>
-      <c r="J77" s="17" t="inlineStr"/>
+      <c r="J77" s="17" t="inlineStr">
+        <is>
+          <t>1-2 words.</t>
+        </is>
+      </c>
       <c r="K77" s="20" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="16" t="inlineStr">
         <is>
-          <t>contact.form.fields.company</t>
+          <t>contact.title</t>
         </is>
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>Contact form</t>
-        </is>
-      </c>
-      <c r="C78" s="17" t="inlineStr">
-        <is>
-          <t>Field label</t>
-        </is>
-      </c>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="C78" s="17" t="inlineStr"/>
       <c r="D78" s="17" t="inlineStr">
         <is>
-          <t>Company (optional)</t>
+          <t>Heading</t>
         </is>
       </c>
       <c r="E78" s="22" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Let's build something intelligent</t>
         </is>
       </c>
       <c r="F78" s="24" t="inlineStr">
@@ -4994,38 +6216,38 @@
         <f>IF(G78="","",LEN(G78))</f>
         <v/>
       </c>
-      <c r="J78" s="17" t="inlineStr"/>
+      <c r="J78" s="17" t="inlineStr">
+        <is>
+          <t>Max ~50 characters.</t>
+        </is>
+      </c>
       <c r="K78" s="20" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
         <is>
-          <t>contact.form.fields.service</t>
+          <t>contact.intro</t>
         </is>
       </c>
       <c r="B79" s="17" t="inlineStr">
         <is>
-          <t>Contact form</t>
-        </is>
-      </c>
-      <c r="C79" s="17" t="inlineStr">
-        <is>
-          <t>Field label</t>
-        </is>
-      </c>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="C79" s="17" t="inlineStr"/>
       <c r="D79" s="17" t="inlineStr">
         <is>
-          <t>Service dropdown</t>
+          <t>Intro paragraph</t>
         </is>
       </c>
       <c r="E79" s="22" t="inlineStr">
         <is>
-          <t>What do you need?</t>
-        </is>
-      </c>
-      <c r="F79" s="24" t="inlineStr">
-        <is>
-          <t>Draft - needs approval</t>
+          <t>Tell us about your idea or the problem you want to solve. A consultant will get back to you to talk through the options. [Placeholder: response time to be confirmed]</t>
+        </is>
+      </c>
+      <c r="F79" s="23" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
         </is>
       </c>
       <c r="G79" s="20" t="n"/>
@@ -5036,55 +6258,32 @@
       </c>
       <c r="J79" s="17" t="inlineStr">
         <is>
-          <t>Options = service names above + 'Not sure yet'.</t>
+          <t>Say how fast you reply, e.g. 'within 1 business day'.</t>
         </is>
       </c>
       <c r="K79" s="20" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="16" t="inlineStr">
-        <is>
-          <t>contact.form.fields.message</t>
-        </is>
-      </c>
-      <c r="B80" s="17" t="inlineStr">
-        <is>
-          <t>Contact form</t>
-        </is>
-      </c>
-      <c r="C80" s="17" t="inlineStr">
-        <is>
-          <t>Field label</t>
-        </is>
-      </c>
-      <c r="D80" s="17" t="inlineStr">
-        <is>
-          <t>Message</t>
-        </is>
-      </c>
-      <c r="E80" s="22" t="inlineStr">
-        <is>
-          <t>Project details</t>
-        </is>
-      </c>
-      <c r="F80" s="24" t="inlineStr">
-        <is>
-          <t>Draft - needs approval</t>
-        </is>
-      </c>
-      <c r="G80" s="20" t="n"/>
-      <c r="H80" s="20" t="n"/>
-      <c r="I80" s="21">
-        <f>IF(G80="","",LEN(G80))</f>
-        <v/>
-      </c>
-      <c r="J80" s="17" t="inlineStr"/>
-      <c r="K80" s="20" t="n"/>
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>CONTACT FORM</t>
+        </is>
+      </c>
+      <c r="B80" s="15" t="n"/>
+      <c r="C80" s="15" t="n"/>
+      <c r="D80" s="15" t="n"/>
+      <c r="E80" s="15" t="n"/>
+      <c r="F80" s="15" t="n"/>
+      <c r="G80" s="15" t="n"/>
+      <c r="H80" s="15" t="n"/>
+      <c r="I80" s="15" t="n"/>
+      <c r="J80" s="15" t="n"/>
+      <c r="K80" s="15" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
         <is>
-          <t>contact.form.fields.messageHint</t>
+          <t>contact.form.title</t>
         </is>
       </c>
       <c r="B81" s="17" t="inlineStr">
@@ -5092,19 +6291,15 @@
           <t>Contact form</t>
         </is>
       </c>
-      <c r="C81" s="17" t="inlineStr">
-        <is>
-          <t>Field hint</t>
-        </is>
-      </c>
+      <c r="C81" s="17" t="inlineStr"/>
       <c r="D81" s="17" t="inlineStr">
         <is>
-          <t>Message hint</t>
+          <t>Form heading</t>
         </is>
       </c>
       <c r="E81" s="22" t="inlineStr">
         <is>
-          <t>A few sentences about your goals, timeline and any systems involved.</t>
+          <t>Send an enquiry</t>
         </is>
       </c>
       <c r="F81" s="24" t="inlineStr">
@@ -5120,7 +6315,7 @@
       </c>
       <c r="J81" s="17" t="inlineStr">
         <is>
-          <t>1 sentence.</t>
+          <t>2-4 words.</t>
         </is>
       </c>
       <c r="K81" s="20" t="n"/>
@@ -5128,7 +6323,7 @@
     <row r="82">
       <c r="A82" s="16" t="inlineStr">
         <is>
-          <t>contact.form.fields.consent</t>
+          <t>contact.form.description</t>
         </is>
       </c>
       <c r="B82" s="17" t="inlineStr">
@@ -5136,24 +6331,20 @@
           <t>Contact form</t>
         </is>
       </c>
-      <c r="C82" s="17" t="inlineStr">
-        <is>
-          <t>Field label</t>
-        </is>
-      </c>
+      <c r="C82" s="17" t="inlineStr"/>
       <c r="D82" s="17" t="inlineStr">
         <is>
-          <t>Consent checkbox</t>
+          <t>Form note</t>
         </is>
       </c>
       <c r="E82" s="22" t="inlineStr">
         <is>
-          <t>[Placeholder] I agree that DigitizWork may use these details to respond to my enquiry, as described in the privacy notice.</t>
-        </is>
-      </c>
-      <c r="F82" s="23" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
+          <t>All fields are required unless marked optional.</t>
+        </is>
+      </c>
+      <c r="F82" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
         </is>
       </c>
       <c r="G82" s="20" t="n"/>
@@ -5164,7 +6355,7 @@
       </c>
       <c r="J82" s="17" t="inlineStr">
         <is>
-          <t>Should match your privacy notice.</t>
+          <t>1 sentence.</t>
         </is>
       </c>
       <c r="K82" s="20" t="n"/>
@@ -5172,7 +6363,7 @@
     <row r="83">
       <c r="A83" s="16" t="inlineStr">
         <is>
-          <t>contact.form.submitLabel</t>
+          <t>contact.form.fields.name</t>
         </is>
       </c>
       <c r="B83" s="17" t="inlineStr">
@@ -5180,15 +6371,19 @@
           <t>Contact form</t>
         </is>
       </c>
-      <c r="C83" s="17" t="inlineStr"/>
+      <c r="C83" s="17" t="inlineStr">
+        <is>
+          <t>Field label</t>
+        </is>
+      </c>
       <c r="D83" s="17" t="inlineStr">
         <is>
-          <t>Submit button</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="E83" s="22" t="inlineStr">
         <is>
-          <t>Send enquiry</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F83" s="24" t="inlineStr">
@@ -5202,134 +6397,422 @@
         <f>IF(G83="","",LEN(G83))</f>
         <v/>
       </c>
-      <c r="J83" s="17" t="inlineStr">
-        <is>
-          <t>2-3 words.</t>
-        </is>
-      </c>
+      <c r="J83" s="17" t="inlineStr"/>
       <c r="K83" s="20" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="14" t="inlineStr">
-        <is>
-          <t>NEW ITEMS (add rows below if you want extra content)</t>
-        </is>
-      </c>
-      <c r="B84" s="15" t="n"/>
-      <c r="C84" s="15" t="n"/>
-      <c r="D84" s="15" t="n"/>
-      <c r="E84" s="15" t="n"/>
-      <c r="F84" s="15" t="n"/>
-      <c r="G84" s="15" t="n"/>
-      <c r="H84" s="15" t="n"/>
-      <c r="I84" s="15" t="n"/>
-      <c r="J84" s="15" t="n"/>
-      <c r="K84" s="15" t="n"/>
+      <c r="A84" s="16" t="inlineStr">
+        <is>
+          <t>contact.form.fields.email</t>
+        </is>
+      </c>
+      <c r="B84" s="17" t="inlineStr">
+        <is>
+          <t>Contact form</t>
+        </is>
+      </c>
+      <c r="C84" s="17" t="inlineStr">
+        <is>
+          <t>Field label</t>
+        </is>
+      </c>
+      <c r="D84" s="17" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E84" s="22" t="inlineStr">
+        <is>
+          <t>Work email</t>
+        </is>
+      </c>
+      <c r="F84" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
+      <c r="G84" s="20" t="n"/>
+      <c r="H84" s="20" t="n"/>
+      <c r="I84" s="21">
+        <f>IF(G84="","",LEN(G84))</f>
+        <v/>
+      </c>
+      <c r="J84" s="17" t="inlineStr"/>
+      <c r="K84" s="20" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="16" t="inlineStr">
         <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="B85" s="20" t="n"/>
-      <c r="C85" s="20" t="n"/>
-      <c r="D85" s="20" t="n"/>
-      <c r="E85" s="17" t="n"/>
-      <c r="F85" s="17" t="n"/>
+          <t>contact.form.fields.company</t>
+        </is>
+      </c>
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>Contact form</t>
+        </is>
+      </c>
+      <c r="C85" s="17" t="inlineStr">
+        <is>
+          <t>Field label</t>
+        </is>
+      </c>
+      <c r="D85" s="17" t="inlineStr">
+        <is>
+          <t>Company (optional)</t>
+        </is>
+      </c>
+      <c r="E85" s="22" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="F85" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
       <c r="G85" s="20" t="n"/>
       <c r="H85" s="20" t="n"/>
       <c r="I85" s="21">
         <f>IF(G85="","",LEN(G85))</f>
         <v/>
       </c>
-      <c r="J85" s="20" t="n"/>
+      <c r="J85" s="17" t="inlineStr"/>
       <c r="K85" s="20" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="16" t="inlineStr">
         <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="B86" s="20" t="n"/>
-      <c r="C86" s="20" t="n"/>
-      <c r="D86" s="20" t="n"/>
-      <c r="E86" s="17" t="n"/>
-      <c r="F86" s="17" t="n"/>
+          <t>contact.form.fields.service</t>
+        </is>
+      </c>
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>Contact form</t>
+        </is>
+      </c>
+      <c r="C86" s="17" t="inlineStr">
+        <is>
+          <t>Field label</t>
+        </is>
+      </c>
+      <c r="D86" s="17" t="inlineStr">
+        <is>
+          <t>Service dropdown</t>
+        </is>
+      </c>
+      <c r="E86" s="22" t="inlineStr">
+        <is>
+          <t>What do you need?</t>
+        </is>
+      </c>
+      <c r="F86" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
       <c r="G86" s="20" t="n"/>
       <c r="H86" s="20" t="n"/>
       <c r="I86" s="21">
         <f>IF(G86="","",LEN(G86))</f>
         <v/>
       </c>
-      <c r="J86" s="20" t="n"/>
+      <c r="J86" s="17" t="inlineStr">
+        <is>
+          <t>Options = service names above + 'Not sure yet'.</t>
+        </is>
+      </c>
       <c r="K86" s="20" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
         <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="B87" s="20" t="n"/>
-      <c r="C87" s="20" t="n"/>
-      <c r="D87" s="20" t="n"/>
-      <c r="E87" s="17" t="n"/>
-      <c r="F87" s="17" t="n"/>
+          <t>contact.form.fields.message</t>
+        </is>
+      </c>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>Contact form</t>
+        </is>
+      </c>
+      <c r="C87" s="17" t="inlineStr">
+        <is>
+          <t>Field label</t>
+        </is>
+      </c>
+      <c r="D87" s="17" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+      <c r="E87" s="22" t="inlineStr">
+        <is>
+          <t>Project details</t>
+        </is>
+      </c>
+      <c r="F87" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
       <c r="G87" s="20" t="n"/>
       <c r="H87" s="20" t="n"/>
       <c r="I87" s="21">
         <f>IF(G87="","",LEN(G87))</f>
         <v/>
       </c>
-      <c r="J87" s="20" t="n"/>
+      <c r="J87" s="17" t="inlineStr"/>
       <c r="K87" s="20" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="16" t="inlineStr">
         <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="B88" s="20" t="n"/>
-      <c r="C88" s="20" t="n"/>
-      <c r="D88" s="20" t="n"/>
-      <c r="E88" s="17" t="n"/>
-      <c r="F88" s="17" t="n"/>
+          <t>contact.form.fields.messageHint</t>
+        </is>
+      </c>
+      <c r="B88" s="17" t="inlineStr">
+        <is>
+          <t>Contact form</t>
+        </is>
+      </c>
+      <c r="C88" s="17" t="inlineStr">
+        <is>
+          <t>Field hint</t>
+        </is>
+      </c>
+      <c r="D88" s="17" t="inlineStr">
+        <is>
+          <t>Message hint</t>
+        </is>
+      </c>
+      <c r="E88" s="22" t="inlineStr">
+        <is>
+          <t>A few sentences about your goals, timeline and any systems involved.</t>
+        </is>
+      </c>
+      <c r="F88" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
       <c r="G88" s="20" t="n"/>
       <c r="H88" s="20" t="n"/>
       <c r="I88" s="21">
         <f>IF(G88="","",LEN(G88))</f>
         <v/>
       </c>
-      <c r="J88" s="20" t="n"/>
+      <c r="J88" s="17" t="inlineStr">
+        <is>
+          <t>1 sentence.</t>
+        </is>
+      </c>
       <c r="K88" s="20" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="16" t="inlineStr">
         <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="B89" s="20" t="n"/>
-      <c r="C89" s="20" t="n"/>
-      <c r="D89" s="20" t="n"/>
-      <c r="E89" s="17" t="n"/>
-      <c r="F89" s="17" t="n"/>
+          <t>contact.form.fields.consent</t>
+        </is>
+      </c>
+      <c r="B89" s="17" t="inlineStr">
+        <is>
+          <t>Contact form</t>
+        </is>
+      </c>
+      <c r="C89" s="17" t="inlineStr">
+        <is>
+          <t>Field label</t>
+        </is>
+      </c>
+      <c r="D89" s="17" t="inlineStr">
+        <is>
+          <t>Consent checkbox</t>
+        </is>
+      </c>
+      <c r="E89" s="22" t="inlineStr">
+        <is>
+          <t>[Placeholder] I agree that DigitizWork may use these details to respond to my enquiry, as described in the privacy notice.</t>
+        </is>
+      </c>
+      <c r="F89" s="23" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
       <c r="G89" s="20" t="n"/>
       <c r="H89" s="20" t="n"/>
       <c r="I89" s="21">
         <f>IF(G89="","",LEN(G89))</f>
         <v/>
       </c>
-      <c r="J89" s="20" t="n"/>
+      <c r="J89" s="17" t="inlineStr">
+        <is>
+          <t>Should match your privacy notice.</t>
+        </is>
+      </c>
       <c r="K89" s="20" t="n"/>
     </row>
+    <row r="90">
+      <c r="A90" s="16" t="inlineStr">
+        <is>
+          <t>contact.form.submitLabel</t>
+        </is>
+      </c>
+      <c r="B90" s="17" t="inlineStr">
+        <is>
+          <t>Contact form</t>
+        </is>
+      </c>
+      <c r="C90" s="17" t="inlineStr"/>
+      <c r="D90" s="17" t="inlineStr">
+        <is>
+          <t>Submit button</t>
+        </is>
+      </c>
+      <c r="E90" s="22" t="inlineStr">
+        <is>
+          <t>Send enquiry</t>
+        </is>
+      </c>
+      <c r="F90" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
+      <c r="G90" s="20" t="n"/>
+      <c r="H90" s="20" t="n"/>
+      <c r="I90" s="21">
+        <f>IF(G90="","",LEN(G90))</f>
+        <v/>
+      </c>
+      <c r="J90" s="17" t="inlineStr">
+        <is>
+          <t>2-3 words.</t>
+        </is>
+      </c>
+      <c r="K90" s="20" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="14" t="inlineStr">
+        <is>
+          <t>NEW ITEMS (add rows below if you want extra content)</t>
+        </is>
+      </c>
+      <c r="B91" s="15" t="n"/>
+      <c r="C91" s="15" t="n"/>
+      <c r="D91" s="15" t="n"/>
+      <c r="E91" s="15" t="n"/>
+      <c r="F91" s="15" t="n"/>
+      <c r="G91" s="15" t="n"/>
+      <c r="H91" s="15" t="n"/>
+      <c r="I91" s="15" t="n"/>
+      <c r="J91" s="15" t="n"/>
+      <c r="K91" s="15" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B92" s="20" t="n"/>
+      <c r="C92" s="20" t="n"/>
+      <c r="D92" s="20" t="n"/>
+      <c r="E92" s="17" t="n"/>
+      <c r="F92" s="17" t="n"/>
+      <c r="G92" s="20" t="n"/>
+      <c r="H92" s="20" t="n"/>
+      <c r="I92" s="21">
+        <f>IF(G92="","",LEN(G92))</f>
+        <v/>
+      </c>
+      <c r="J92" s="20" t="n"/>
+      <c r="K92" s="20" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B93" s="20" t="n"/>
+      <c r="C93" s="20" t="n"/>
+      <c r="D93" s="20" t="n"/>
+      <c r="E93" s="17" t="n"/>
+      <c r="F93" s="17" t="n"/>
+      <c r="G93" s="20" t="n"/>
+      <c r="H93" s="20" t="n"/>
+      <c r="I93" s="21">
+        <f>IF(G93="","",LEN(G93))</f>
+        <v/>
+      </c>
+      <c r="J93" s="20" t="n"/>
+      <c r="K93" s="20" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B94" s="20" t="n"/>
+      <c r="C94" s="20" t="n"/>
+      <c r="D94" s="20" t="n"/>
+      <c r="E94" s="17" t="n"/>
+      <c r="F94" s="17" t="n"/>
+      <c r="G94" s="20" t="n"/>
+      <c r="H94" s="20" t="n"/>
+      <c r="I94" s="21">
+        <f>IF(G94="","",LEN(G94))</f>
+        <v/>
+      </c>
+      <c r="J94" s="20" t="n"/>
+      <c r="K94" s="20" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B95" s="20" t="n"/>
+      <c r="C95" s="20" t="n"/>
+      <c r="D95" s="20" t="n"/>
+      <c r="E95" s="17" t="n"/>
+      <c r="F95" s="17" t="n"/>
+      <c r="G95" s="20" t="n"/>
+      <c r="H95" s="20" t="n"/>
+      <c r="I95" s="21">
+        <f>IF(G95="","",LEN(G95))</f>
+        <v/>
+      </c>
+      <c r="J95" s="20" t="n"/>
+      <c r="K95" s="20" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B96" s="20" t="n"/>
+      <c r="C96" s="20" t="n"/>
+      <c r="D96" s="20" t="n"/>
+      <c r="E96" s="17" t="n"/>
+      <c r="F96" s="17" t="n"/>
+      <c r="G96" s="20" t="n"/>
+      <c r="H96" s="20" t="n"/>
+      <c r="I96" s="21">
+        <f>IF(G96="","",LEN(G96))</f>
+        <v/>
+      </c>
+      <c r="J96" s="20" t="n"/>
+      <c r="K96" s="20" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K89"/>
+  <autoFilter ref="A1:K96"/>
   <dataValidations count="1">
-    <dataValidation sqref="H3 H4 H5 H6 H7 H8 H9 H10 H11 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H48 H49 H50 H51 H52 H53 H54 H55 H56 H57 H58 H59 H60 H61 H62 H64 H65 H66 H67 H68 H70 H71 H72 H74 H75 H76 H77 H78 H79 H80 H81 H82 H83 H85 H86 H87 H88 H89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H3 H4 H5 H6 H7 H8 H9 H10 H11 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H48 H49 H50 H51 H52 H53 H54 H55 H56 H57 H58 H59 H60 H61 H62 H64 H65 H66 H67 H68 H70 H71 H72 H73 H74 H75 H77 H78 H79 H81 H82 H83 H84 H85 H86 H87 H88 H89 H90 H92 H93 H94 H95 H96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Keep as is,Replace with new content,Remove,Approve current text"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6579,269 +8062,1327 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="35" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Field ID</t>
         </is>
       </c>
       <c r="B1" s="13" t="inlineStr">
         <is>
-          <t>Show on site? (Yes/No)</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="C1" s="13" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="D1" s="13" t="inlineStr">
         <is>
-          <t>Job title / role</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="E1" s="13" t="inlineStr">
         <is>
-          <t>Short bio (2-3 sentences)</t>
+          <t>Current content</t>
         </is>
       </c>
       <c r="F1" s="13" t="inlineStr">
         <is>
-          <t>Specialisms (comma-separated)</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="G1" s="13" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>New content</t>
         </is>
       </c>
       <c r="H1" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn URL</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="I1" s="13" t="inlineStr">
         <is>
-          <t>Photo file name</t>
+          <t>Characters (new)</t>
         </is>
       </c>
       <c r="J1" s="13" t="inlineStr">
         <is>
-          <t>Consent to publish (Yes/No)</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="K1" s="13" t="inlineStr">
         <is>
-          <t>Bio characters</t>
-        </is>
-      </c>
-      <c r="L1" s="13" t="inlineStr">
-        <is>
           <t>Notes for Claude</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="20" t="n"/>
-      <c r="C2" s="20" t="n"/>
-      <c r="D2" s="20" t="n"/>
-      <c r="E2" s="20" t="n"/>
-      <c r="F2" s="20" t="n"/>
-      <c r="G2" s="20" t="n"/>
-      <c r="H2" s="20" t="n"/>
-      <c r="I2" s="20" t="n"/>
-      <c r="J2" s="20" t="n"/>
-      <c r="K2" s="21">
-        <f>IF(E2="","",LEN(E2))</f>
-        <v/>
-      </c>
-      <c r="L2" s="20" t="inlineStr">
-        <is>
-          <t>Site currently shows 4 placeholder cards. Add as many people as you need.</t>
-        </is>
-      </c>
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>HERO</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+      <c r="J2" s="15" t="n"/>
+      <c r="K2" s="15" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="20" t="n"/>
-      <c r="C3" s="20" t="n"/>
-      <c r="D3" s="20" t="n"/>
-      <c r="E3" s="20" t="n"/>
-      <c r="F3" s="20" t="n"/>
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.hero.eyebrow</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr"/>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>Small label</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t>Our clients</t>
+        </is>
+      </c>
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
       <c r="G3" s="20" t="n"/>
       <c r="H3" s="20" t="n"/>
-      <c r="I3" s="20" t="n"/>
-      <c r="J3" s="20" t="n"/>
-      <c r="K3" s="21">
-        <f>IF(E3="","",LEN(E3))</f>
-        <v/>
-      </c>
-      <c r="L3" s="20" t="n"/>
+      <c r="I3" s="21">
+        <f>IF(G3="","",LEN(G3))</f>
+        <v/>
+      </c>
+      <c r="J3" s="17" t="inlineStr">
+        <is>
+          <t>2-3 words.</t>
+        </is>
+      </c>
+      <c r="K3" s="20" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="20" t="n"/>
-      <c r="C4" s="20" t="n"/>
-      <c r="D4" s="20" t="n"/>
-      <c r="E4" s="20" t="n"/>
-      <c r="F4" s="20" t="n"/>
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.hero.title</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr"/>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Heading (part 1)</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>Organisations we</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
       <c r="G4" s="20" t="n"/>
       <c r="H4" s="20" t="n"/>
-      <c r="I4" s="20" t="n"/>
-      <c r="J4" s="20" t="n"/>
-      <c r="K4" s="21">
-        <f>IF(E4="","",LEN(E4))</f>
-        <v/>
-      </c>
-      <c r="L4" s="20" t="n"/>
+      <c r="I4" s="21">
+        <f>IF(G4="","",LEN(G4))</f>
+        <v/>
+      </c>
+      <c r="J4" s="17" t="inlineStr">
+        <is>
+          <t>Max ~40 characters.</t>
+        </is>
+      </c>
+      <c r="K4" s="20" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="20" t="n"/>
-      <c r="C5" s="20" t="n"/>
-      <c r="D5" s="20" t="n"/>
-      <c r="E5" s="20" t="n"/>
-      <c r="F5" s="20" t="n"/>
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.hero.titleHighlight</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr"/>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>Heading (part 2, gradient colour)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>build with.</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
       <c r="G5" s="20" t="n"/>
       <c r="H5" s="20" t="n"/>
-      <c r="I5" s="20" t="n"/>
-      <c r="J5" s="20" t="n"/>
-      <c r="K5" s="21">
-        <f>IF(E5="","",LEN(E5))</f>
-        <v/>
-      </c>
-      <c r="L5" s="20" t="n"/>
+      <c r="I5" s="21">
+        <f>IF(G5="","",LEN(G5))</f>
+        <v/>
+      </c>
+      <c r="J5" s="17" t="inlineStr">
+        <is>
+          <t>Max ~40 characters.</t>
+        </is>
+      </c>
+      <c r="K5" s="20" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="20" t="n"/>
-      <c r="C6" s="20" t="n"/>
-      <c r="D6" s="20" t="n"/>
-      <c r="E6" s="20" t="n"/>
-      <c r="F6" s="20" t="n"/>
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.hero.lead</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr"/>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>Intro paragraph</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>[Placeholder] A short introduction to the organisations DigitizWork works with. Client names, logos and stories appear here only with each client's permission.</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
       <c r="G6" s="20" t="n"/>
       <c r="H6" s="20" t="n"/>
-      <c r="I6" s="20" t="n"/>
-      <c r="J6" s="20" t="n"/>
-      <c r="K6" s="21">
-        <f>IF(E6="","",LEN(E6))</f>
-        <v/>
-      </c>
-      <c r="L6" s="20" t="n"/>
+      <c r="I6" s="21">
+        <f>IF(G6="","",LEN(G6))</f>
+        <v/>
+      </c>
+      <c r="J6" s="17" t="inlineStr">
+        <is>
+          <t>1-2 sentences.</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="20" t="n"/>
-      <c r="C7" s="20" t="n"/>
-      <c r="D7" s="20" t="n"/>
-      <c r="E7" s="20" t="n"/>
-      <c r="F7" s="20" t="n"/>
-      <c r="G7" s="20" t="n"/>
-      <c r="H7" s="20" t="n"/>
-      <c r="I7" s="20" t="n"/>
-      <c r="J7" s="20" t="n"/>
-      <c r="K7" s="21">
-        <f>IF(E7="","",LEN(E7))</f>
-        <v/>
-      </c>
-      <c r="L7" s="20" t="n"/>
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>WHO WE HELP</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="n"/>
+      <c r="E7" s="15" t="n"/>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n"/>
+      <c r="I7" s="15" t="n"/>
+      <c r="J7" s="15" t="n"/>
+      <c r="K7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="20" t="n"/>
-      <c r="C8" s="20" t="n"/>
-      <c r="D8" s="20" t="n"/>
-      <c r="E8" s="20" t="n"/>
-      <c r="F8" s="20" t="n"/>
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.intro.eyebrow</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Who we help</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr"/>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>Small label</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>Who we help</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
       <c r="G8" s="20" t="n"/>
       <c r="H8" s="20" t="n"/>
-      <c r="I8" s="20" t="n"/>
-      <c r="J8" s="20" t="n"/>
-      <c r="K8" s="21">
-        <f>IF(E8="","",LEN(E8))</f>
-        <v/>
-      </c>
-      <c r="L8" s="20" t="n"/>
+      <c r="I8" s="21">
+        <f>IF(G8="","",LEN(G8))</f>
+        <v/>
+      </c>
+      <c r="J8" s="17" t="inlineStr">
+        <is>
+          <t>2-3 words.</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="20" t="n"/>
-      <c r="C9" s="20" t="n"/>
-      <c r="D9" s="20" t="n"/>
-      <c r="E9" s="20" t="n"/>
-      <c r="F9" s="20" t="n"/>
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.intro.title</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Who we help</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr"/>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>[Placeholder] The kinds of organisations we help</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
       <c r="G9" s="20" t="n"/>
       <c r="H9" s="20" t="n"/>
-      <c r="I9" s="20" t="n"/>
-      <c r="J9" s="20" t="n"/>
-      <c r="K9" s="21">
-        <f>IF(E9="","",LEN(E9))</f>
-        <v/>
-      </c>
-      <c r="L9" s="20" t="n"/>
+      <c r="I9" s="21">
+        <f>IF(G9="","",LEN(G9))</f>
+        <v/>
+      </c>
+      <c r="J9" s="17" t="inlineStr">
+        <is>
+          <t>Max ~50 characters.</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.intro.paragraphs.1</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Who we help</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr"/>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>Paragraph 1</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>[Placeholder] Describe the kinds of organisations DigitizWork helps, for example by size, sector or stage, using only facts the owner has confirmed.</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="20" t="n"/>
+      <c r="I10" s="21">
+        <f>IF(G10="","",LEN(G10))</f>
+        <v/>
+      </c>
+      <c r="J10" s="17" t="inlineStr">
+        <is>
+          <t>2-3 sentences.</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.intro.paragraphs.2</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Who we help</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr"/>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>Paragraph 2</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>[Placeholder] Describe the typical problems these organisations bring to DigitizWork and how AI-powered software helps.</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="n"/>
+      <c r="H11" s="20" t="n"/>
+      <c r="I11" s="21">
+        <f>IF(G11="","",LEN(G11))</f>
+        <v/>
+      </c>
+      <c r="J11" s="17" t="inlineStr">
+        <is>
+          <t>2-3 sentences.</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Photos:</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Square, at least 800 x 800 px, JPG/PNG/WebP. Send the files with this sheet and put the file name in 'Photo file name'.</t>
-        </is>
-      </c>
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>TYPICAL CLIENTS</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="15" t="n"/>
+      <c r="H12" s="15" t="n"/>
+      <c r="I12" s="15" t="n"/>
+      <c r="J12" s="15" t="n"/>
+      <c r="K12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Consent:</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Each person must agree to their name, bio and photo being published. Cards without 'Yes' are not shown.</t>
-        </is>
-      </c>
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.audiences.eyebrow</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Typical clients</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr"/>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>Small label</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>Typical clients</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="n"/>
+      <c r="H13" s="20" t="n"/>
+      <c r="I13" s="21">
+        <f>IF(G13="","",LEN(G13))</f>
+        <v/>
+      </c>
+      <c r="J13" s="17" t="inlineStr">
+        <is>
+          <t>2-3 words.</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.audiences.title</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Typical clients</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr"/>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>[Placeholder] Who we typically work with</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="n"/>
+      <c r="H14" s="20" t="n"/>
+      <c r="I14" s="21">
+        <f>IF(G14="","",LEN(G14))</f>
+        <v/>
+      </c>
+      <c r="J14" s="17" t="inlineStr">
+        <is>
+          <t>Max ~50 characters.</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.audiences.items.1.title</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Typical clients</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>[Placeholder] Organisation type 1</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="n"/>
+      <c r="H15" s="20" t="n"/>
+      <c r="I15" s="21">
+        <f>IF(G15="","",LEN(G15))</f>
+        <v/>
+      </c>
+      <c r="J15" s="17" t="inlineStr">
+        <is>
+          <t>2-4 words, e.g. 'Small businesses'.</t>
+        </is>
+      </c>
+      <c r="K15" s="20" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.audiences.items.1.description</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Typical clients</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>[Placeholder] One sentence on how DigitizWork helps this kind of organisation.</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="n"/>
+      <c r="H16" s="20" t="n"/>
+      <c r="I16" s="21">
+        <f>IF(G16="","",LEN(G16))</f>
+        <v/>
+      </c>
+      <c r="J16" s="17" t="inlineStr">
+        <is>
+          <t>1 sentence.</t>
+        </is>
+      </c>
+      <c r="K16" s="20" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.audiences.items.2.title</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Typical clients</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>Type 2</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>[Placeholder] Organisation type 2</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="n"/>
+      <c r="H17" s="20" t="n"/>
+      <c r="I17" s="21">
+        <f>IF(G17="","",LEN(G17))</f>
+        <v/>
+      </c>
+      <c r="J17" s="17" t="inlineStr">
+        <is>
+          <t>2-4 words, e.g. 'Small businesses'.</t>
+        </is>
+      </c>
+      <c r="K17" s="20" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.audiences.items.2.description</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Typical clients</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>Type 2</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>[Placeholder] One sentence on how DigitizWork helps this kind of organisation.</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="n"/>
+      <c r="H18" s="20" t="n"/>
+      <c r="I18" s="21">
+        <f>IF(G18="","",LEN(G18))</f>
+        <v/>
+      </c>
+      <c r="J18" s="17" t="inlineStr">
+        <is>
+          <t>1 sentence.</t>
+        </is>
+      </c>
+      <c r="K18" s="20" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.audiences.items.3.title</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Typical clients</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Type 3</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>[Placeholder] Organisation type 3</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="n"/>
+      <c r="H19" s="20" t="n"/>
+      <c r="I19" s="21">
+        <f>IF(G19="","",LEN(G19))</f>
+        <v/>
+      </c>
+      <c r="J19" s="17" t="inlineStr">
+        <is>
+          <t>2-4 words, e.g. 'Small businesses'.</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.audiences.items.3.description</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Typical clients</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Type 3</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>[Placeholder] One sentence on how DigitizWork helps this kind of organisation.</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="n"/>
+      <c r="H20" s="20" t="n"/>
+      <c r="I20" s="21">
+        <f>IF(G20="","",LEN(G20))</f>
+        <v/>
+      </c>
+      <c r="J20" s="17" t="inlineStr">
+        <is>
+          <t>1 sentence.</t>
+        </is>
+      </c>
+      <c r="K20" s="20" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>CLIENT LIST</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="15" t="n"/>
+      <c r="H21" s="15" t="n"/>
+      <c r="I21" s="15" t="n"/>
+      <c r="J21" s="15" t="n"/>
+      <c r="K21" s="15" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.clientList.eyebrow</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>Client list</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr"/>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>Small label</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>Client list</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="n"/>
+      <c r="H22" s="20" t="n"/>
+      <c r="I22" s="21">
+        <f>IF(G22="","",LEN(G22))</f>
+        <v/>
+      </c>
+      <c r="J22" s="17" t="inlineStr">
+        <is>
+          <t>2-3 words.</t>
+        </is>
+      </c>
+      <c r="K22" s="20" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.clientList.title</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>Client list</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr"/>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>Some of the organisations we work with</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="n"/>
+      <c r="H23" s="20" t="n"/>
+      <c r="I23" s="21">
+        <f>IF(G23="","",LEN(G23))</f>
+        <v/>
+      </c>
+      <c r="J23" s="17" t="inlineStr">
+        <is>
+          <t>Max ~50 characters. Clients themselves go in the 'Clients' tab.</t>
+        </is>
+      </c>
+      <c r="K23" s="20" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.clientList.intro</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>Client list</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr"/>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>Shown with each client's permission.</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="n"/>
+      <c r="H24" s="20" t="n"/>
+      <c r="I24" s="21">
+        <f>IF(G24="","",LEN(G24))</f>
+        <v/>
+      </c>
+      <c r="J24" s="17" t="inlineStr">
+        <is>
+          <t>1 sentence.</t>
+        </is>
+      </c>
+      <c r="K24" s="20" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>CASE STUDIES</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="n"/>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="15" t="n"/>
+      <c r="E25" s="15" t="n"/>
+      <c r="F25" s="15" t="n"/>
+      <c r="G25" s="15" t="n"/>
+      <c r="H25" s="15" t="n"/>
+      <c r="I25" s="15" t="n"/>
+      <c r="J25" s="15" t="n"/>
+      <c r="K25" s="15" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.caseStudies.eyebrow</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>Case studies</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr"/>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>Small label</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>Case studies</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="n"/>
+      <c r="H26" s="20" t="n"/>
+      <c r="I26" s="21">
+        <f>IF(G26="","",LEN(G26))</f>
+        <v/>
+      </c>
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>2-3 words.</t>
+        </is>
+      </c>
+      <c r="K26" s="20" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.caseStudies.title</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>Case studies</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr"/>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>[Placeholder] Selected client stories</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="n"/>
+      <c r="H27" s="20" t="n"/>
+      <c r="I27" s="21">
+        <f>IF(G27="","",LEN(G27))</f>
+        <v/>
+      </c>
+      <c r="J27" s="17" t="inlineStr">
+        <is>
+          <t>Max ~50 characters. Stories go in the 'Case studies' tab.</t>
+        </is>
+      </c>
+      <c r="K27" s="20" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.caseStudies.intro</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>Case studies</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr"/>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>[Placeholder] Short summaries of real projects, published with each client's approval.</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="n"/>
+      <c r="H28" s="20" t="n"/>
+      <c r="I28" s="21">
+        <f>IF(G28="","",LEN(G28))</f>
+        <v/>
+      </c>
+      <c r="J28" s="17" t="inlineStr">
+        <is>
+          <t>1 sentence.</t>
+        </is>
+      </c>
+      <c r="K28" s="20" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>CALL TO ACTION</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n"/>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="15" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="15" t="n"/>
+      <c r="H29" s="15" t="n"/>
+      <c r="I29" s="15" t="n"/>
+      <c r="J29" s="15" t="n"/>
+      <c r="K29" s="15" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.cta.title</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>Call to action</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr"/>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>Could your organisation be next?</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="n"/>
+      <c r="H30" s="20" t="n"/>
+      <c r="I30" s="21">
+        <f>IF(G30="","",LEN(G30))</f>
+        <v/>
+      </c>
+      <c r="J30" s="17" t="inlineStr">
+        <is>
+          <t>2-6 words.</t>
+        </is>
+      </c>
+      <c r="K30" s="20" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.cta.text</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Call to action</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr"/>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>[Placeholder] Tell us what you want to build and we will talk through the options.</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="n"/>
+      <c r="H31" s="20" t="n"/>
+      <c r="I31" s="21">
+        <f>IF(G31="","",LEN(G31))</f>
+        <v/>
+      </c>
+      <c r="J31" s="17" t="inlineStr">
+        <is>
+          <t>1 sentence.</t>
+        </is>
+      </c>
+      <c r="K31" s="20" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>clientsPage.cta.button</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>Call to action</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr"/>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>Start a project</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="n"/>
+      <c r="H32" s="20" t="n"/>
+      <c r="I32" s="21">
+        <f>IF(G32="","",LEN(G32))</f>
+        <v/>
+      </c>
+      <c r="J32" s="17" t="inlineStr">
+        <is>
+          <t>2-4 words.</t>
+        </is>
+      </c>
+      <c r="K32" s="20" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>NEW ITEMS (add rows below if you want extra content)</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="15" t="n"/>
+      <c r="D33" s="15" t="n"/>
+      <c r="E33" s="15" t="n"/>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="15" t="n"/>
+      <c r="H33" s="15" t="n"/>
+      <c r="I33" s="15" t="n"/>
+      <c r="J33" s="15" t="n"/>
+      <c r="K33" s="15" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="n"/>
+      <c r="C34" s="20" t="n"/>
+      <c r="D34" s="20" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
+      <c r="G34" s="20" t="n"/>
+      <c r="H34" s="20" t="n"/>
+      <c r="I34" s="21">
+        <f>IF(G34="","",LEN(G34))</f>
+        <v/>
+      </c>
+      <c r="J34" s="20" t="n"/>
+      <c r="K34" s="20" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="n"/>
+      <c r="C35" s="20" t="n"/>
+      <c r="D35" s="20" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
+      <c r="G35" s="20" t="n"/>
+      <c r="H35" s="20" t="n"/>
+      <c r="I35" s="21">
+        <f>IF(G35="","",LEN(G35))</f>
+        <v/>
+      </c>
+      <c r="J35" s="20" t="n"/>
+      <c r="K35" s="20" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="n"/>
+      <c r="C36" s="20" t="n"/>
+      <c r="D36" s="20" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="17" t="n"/>
+      <c r="G36" s="20" t="n"/>
+      <c r="H36" s="20" t="n"/>
+      <c r="I36" s="21">
+        <f>IF(G36="","",LEN(G36))</f>
+        <v/>
+      </c>
+      <c r="J36" s="20" t="n"/>
+      <c r="K36" s="20" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="n"/>
+      <c r="C37" s="20" t="n"/>
+      <c r="D37" s="20" t="n"/>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="17" t="n"/>
+      <c r="G37" s="20" t="n"/>
+      <c r="H37" s="20" t="n"/>
+      <c r="I37" s="21">
+        <f>IF(G37="","",LEN(G37))</f>
+        <v/>
+      </c>
+      <c r="J37" s="20" t="n"/>
+      <c r="K37" s="20" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="n"/>
+      <c r="C38" s="20" t="n"/>
+      <c r="D38" s="20" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="17" t="n"/>
+      <c r="G38" s="20" t="n"/>
+      <c r="H38" s="20" t="n"/>
+      <c r="I38" s="21">
+        <f>IF(G38="","",LEN(G38))</f>
+        <v/>
+      </c>
+      <c r="J38" s="20" t="n"/>
+      <c r="K38" s="20" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K38"/>
   <dataValidations count="1">
-    <dataValidation sqref="B2 B3 B4 B5 B6 B7 B8 B9 J2 J3 J4 J5 J6 J7 J8 J9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
+    <dataValidation sqref="H3 H4 H5 H6 H8 H9 H10 H11 H13 H14 H15 H16 H17 H18 H19 H20 H22 H23 H24 H26 H27 H28 H30 H31 H32 H34 H35 H36 H37 H38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Keep as is,Replace with new content,Remove,Approve current text"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6854,321 +9395,789 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="35" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>Image slot</t>
+          <t>Field ID</t>
         </is>
       </c>
       <c r="B1" s="13" t="inlineStr">
         <is>
-          <t>Where it appears</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="C1" s="13" t="inlineStr">
         <is>
-          <t>Current file</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="D1" s="13" t="inlineStr">
         <is>
-          <t>Description (alt text)</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="E1" s="13" t="inlineStr">
         <is>
-          <t>New image file name</t>
+          <t>Current content</t>
         </is>
       </c>
       <c r="F1" s="13" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>New content</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="G1" s="13" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Characters (new)</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
         <is>
           <t>Notes for Claude</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>heroAiCore</t>
-        </is>
-      </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>Home - hero</t>
-        </is>
-      </c>
-      <c r="C2" s="22" t="inlineStr">
-        <is>
-          <t>/images/hero/ai-core.svg</t>
-        </is>
-      </c>
-      <c r="D2" s="22" t="inlineStr">
-        <is>
-          <t>Illustration of an AI core connected to a network of nodes, surrounded by panels showing code, a chat conversation and a data chart.</t>
-        </is>
-      </c>
-      <c r="E2" s="20" t="n"/>
-      <c r="F2" s="20" t="n"/>
-      <c r="G2" s="20" t="n"/>
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>HERO</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+      <c r="J2" s="15" t="n"/>
+      <c r="K2" s="15" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
-        <is>
-          <t>serviceWebMobile</t>
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>testimonialsPage.hero.eyebrow</t>
         </is>
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>Home - Service 1</t>
-        </is>
-      </c>
-      <c r="C3" s="22" t="inlineStr">
-        <is>
-          <t>/images/services/web-mobile.svg</t>
-        </is>
-      </c>
-      <c r="D3" s="22" t="inlineStr">
-        <is>
-          <t>Illustration of a web browser window and a mobile phone showing an app interface.</t>
-        </is>
-      </c>
-      <c r="E3" s="20" t="n"/>
-      <c r="F3" s="20" t="n"/>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr"/>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>Small label</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t>Client feedback</t>
+        </is>
+      </c>
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
       <c r="G3" s="20" t="n"/>
+      <c r="H3" s="20" t="n"/>
+      <c r="I3" s="21">
+        <f>IF(G3="","",LEN(G3))</f>
+        <v/>
+      </c>
+      <c r="J3" s="17" t="inlineStr">
+        <is>
+          <t>2-3 words.</t>
+        </is>
+      </c>
+      <c r="K3" s="20" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>serviceAiAssistants</t>
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>testimonialsPage.hero.title</t>
         </is>
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>Home - Service 2</t>
-        </is>
-      </c>
-      <c r="C4" s="22" t="inlineStr">
-        <is>
-          <t>/images/services/ai-assistants.svg</t>
-        </is>
-      </c>
-      <c r="D4" s="22" t="inlineStr">
-        <is>
-          <t>Illustration of a chat conversation between a person and a glowing AI assistant.</t>
-        </is>
-      </c>
-      <c r="E4" s="20" t="n"/>
-      <c r="F4" s="20" t="n"/>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr"/>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Heading (part 1)</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>What our clients</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
       <c r="G4" s="20" t="n"/>
+      <c r="H4" s="20" t="n"/>
+      <c r="I4" s="21">
+        <f>IF(G4="","",LEN(G4))</f>
+        <v/>
+      </c>
+      <c r="J4" s="17" t="inlineStr">
+        <is>
+          <t>Max ~40 characters.</t>
+        </is>
+      </c>
+      <c r="K4" s="20" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>serviceAutomation</t>
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>testimonialsPage.hero.titleHighlight</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>Home - Service 3</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>/images/services/automation.svg</t>
-        </is>
-      </c>
-      <c r="D5" s="22" t="inlineStr">
-        <is>
-          <t>Illustration of documents flowing through an AI node and coming out as completed tasks.</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="n"/>
-      <c r="F5" s="20" t="n"/>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr"/>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>Heading (part 2, gradient colour)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>say about working with us.</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
       <c r="G5" s="20" t="n"/>
+      <c r="H5" s="20" t="n"/>
+      <c r="I5" s="21">
+        <f>IF(G5="","",LEN(G5))</f>
+        <v/>
+      </c>
+      <c r="J5" s="17" t="inlineStr">
+        <is>
+          <t>Max ~40 characters.</t>
+        </is>
+      </c>
+      <c r="K5" s="20" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>serviceDataAnalytics</t>
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>testimonialsPage.hero.lead</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>Home - Service 4</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>/images/services/data-analytics.svg</t>
-        </is>
-      </c>
-      <c r="D6" s="22" t="inlineStr">
-        <is>
-          <t>Illustration of a dashboard with a bar chart, a trend line and a ring chart.</t>
-        </is>
-      </c>
-      <c r="E6" s="20" t="n"/>
-      <c r="F6" s="20" t="n"/>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr"/>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>Intro paragraph</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>[Placeholder] Feedback from the organisations DigitizWork works with, published only with each person's written consent.</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
       <c r="G6" s="20" t="n"/>
+      <c r="H6" s="20" t="n"/>
+      <c r="I6" s="21">
+        <f>IF(G6="","",LEN(G6))</f>
+        <v/>
+      </c>
+      <c r="J6" s="17" t="inlineStr">
+        <is>
+          <t>1-2 sentences.</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>serviceCloudIntegration</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Home - Service 5</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>/images/services/cloud-integration.svg</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>Illustration of a cloud connected to several application blocks.</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="n"/>
-      <c r="F7" s="20" t="n"/>
-      <c r="G7" s="20" t="n"/>
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>FEEDBACK LIST</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="n"/>
+      <c r="E7" s="15" t="n"/>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n"/>
+      <c r="I7" s="15" t="n"/>
+      <c r="J7" s="15" t="n"/>
+      <c r="K7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>serviceCustomSoftware</t>
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>testimonialsPage.list.eyebrow</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>Home - Service 6</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>/images/services/custom-software.svg</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>Illustration of layered code editor windows with code brackets.</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="n"/>
-      <c r="F8" s="20" t="n"/>
+          <t>Feedback list</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr"/>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>Small label</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
       <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20" t="n"/>
+      <c r="I8" s="21">
+        <f>IF(G8="","",LEN(G8))</f>
+        <v/>
+      </c>
+      <c r="J8" s="17" t="inlineStr">
+        <is>
+          <t>1-2 words.</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>aboutCollaboration</t>
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>testimonialsPage.list.title</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Home - About section</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>/images/about/collaboration.svg</t>
-        </is>
-      </c>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>Illustration of people connected around a central AI node, representing consultants working with AI.</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="n"/>
-      <c r="F9" s="20" t="n"/>
+          <t>Feedback list</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr"/>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>In our clients' words</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
       <c r="G9" s="20" t="n"/>
+      <c r="H9" s="20" t="n"/>
+      <c r="I9" s="21">
+        <f>IF(G9="","",LEN(G9))</f>
+        <v/>
+      </c>
+      <c r="J9" s="17" t="inlineStr">
+        <is>
+          <t>Max ~50 characters. Quotes go in the 'Testimonials' tab.</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>aboutTeamNetwork</t>
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>testimonialsPage.list.intro</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>About page - hero</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>/images/about/team-network.svg</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="inlineStr">
-        <is>
-          <t>Illustration of a network of people linked together around a glowing core.</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="n"/>
-      <c r="F10" s="20" t="n"/>
+          <t>Feedback list</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr"/>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>Every quote is published with the client's written consent.</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
       <c r="G10" s="20" t="n"/>
+      <c r="H10" s="20" t="n"/>
+      <c r="I10" s="21">
+        <f>IF(G10="","",LEN(G10))</f>
+        <v/>
+      </c>
+      <c r="J10" s="17" t="inlineStr">
+        <is>
+          <t>1 sentence.</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>consultantPlaceholder</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>About page - consultant without photo</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>/images/team/avatar-placeholder.svg</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="inlineStr">
-        <is>
-          <t>(decorative)</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="n"/>
-      <c r="F11" s="20" t="n"/>
-      <c r="G11" s="20" t="n"/>
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>SHARE FEEDBACK</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="15" t="n"/>
+      <c r="I11" s="15" t="n"/>
+      <c r="J11" s="15" t="n"/>
+      <c r="K11" s="15" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>testimonialsPage.share.title</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Share feedback</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr"/>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>Worked with us? Share your feedback</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
+      <c r="I12" s="21">
+        <f>IF(G12="","",LEN(G12))</f>
+        <v/>
+      </c>
+      <c r="J12" s="17" t="inlineStr">
+        <is>
+          <t>Max ~50 characters.</t>
+        </is>
+      </c>
+      <c r="K12" s="20" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Note:</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Ready-made AI image prompts and sizes for each slot are in docs/frontend/image-prompts.md. Do not use AI-generated faces for real consultants. Record the licence/terms of any image you supply.</t>
-        </is>
-      </c>
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>testimonialsPage.share.text</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Share feedback</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr"/>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>[Placeholder] We would love to hear how your project went. Send us a message and we will ask for your consent before publishing anything.</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="n"/>
+      <c r="H13" s="20" t="n"/>
+      <c r="I13" s="21">
+        <f>IF(G13="","",LEN(G13))</f>
+        <v/>
+      </c>
+      <c r="J13" s="17" t="inlineStr">
+        <is>
+          <t>1-2 sentences.</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>testimonialsPage.share.button</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Share feedback</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr"/>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>Share your feedback</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="n"/>
+      <c r="H14" s="20" t="n"/>
+      <c r="I14" s="21">
+        <f>IF(G14="","",LEN(G14))</f>
+        <v/>
+      </c>
+      <c r="J14" s="17" t="inlineStr">
+        <is>
+          <t>2-4 words.</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>CALL TO ACTION</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="15" t="n"/>
+      <c r="G15" s="15" t="n"/>
+      <c r="H15" s="15" t="n"/>
+      <c r="I15" s="15" t="n"/>
+      <c r="J15" s="15" t="n"/>
+      <c r="K15" s="15" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>testimonialsPage.cta.title</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Call to action</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr"/>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>Ready to start your project?</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="n"/>
+      <c r="H16" s="20" t="n"/>
+      <c r="I16" s="21">
+        <f>IF(G16="","",LEN(G16))</f>
+        <v/>
+      </c>
+      <c r="J16" s="17" t="inlineStr">
+        <is>
+          <t>2-6 words.</t>
+        </is>
+      </c>
+      <c r="K16" s="20" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>testimonialsPage.cta.text</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Call to action</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr"/>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>[Placeholder] Tell us what you want to build. A consultant will get back to you.</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="n"/>
+      <c r="H17" s="20" t="n"/>
+      <c r="I17" s="21">
+        <f>IF(G17="","",LEN(G17))</f>
+        <v/>
+      </c>
+      <c r="J17" s="17" t="inlineStr">
+        <is>
+          <t>1 sentence.</t>
+        </is>
+      </c>
+      <c r="K17" s="20" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>testimonialsPage.cta.button</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Call to action</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr"/>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>Start a project</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Draft - needs approval</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="n"/>
+      <c r="H18" s="20" t="n"/>
+      <c r="I18" s="21">
+        <f>IF(G18="","",LEN(G18))</f>
+        <v/>
+      </c>
+      <c r="J18" s="17" t="inlineStr">
+        <is>
+          <t>2-4 words.</t>
+        </is>
+      </c>
+      <c r="K18" s="20" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>NEW ITEMS (add rows below if you want extra content)</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="15" t="n"/>
+      <c r="H19" s="15" t="n"/>
+      <c r="I19" s="15" t="n"/>
+      <c r="J19" s="15" t="n"/>
+      <c r="K19" s="15" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="n"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
+      <c r="G20" s="20" t="n"/>
+      <c r="H20" s="20" t="n"/>
+      <c r="I20" s="21">
+        <f>IF(G20="","",LEN(G20))</f>
+        <v/>
+      </c>
+      <c r="J20" s="20" t="n"/>
+      <c r="K20" s="20" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="n"/>
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="20" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
+      <c r="G21" s="20" t="n"/>
+      <c r="H21" s="20" t="n"/>
+      <c r="I21" s="21">
+        <f>IF(G21="","",LEN(G21))</f>
+        <v/>
+      </c>
+      <c r="J21" s="20" t="n"/>
+      <c r="K21" s="20" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="n"/>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="20" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
+      <c r="G22" s="20" t="n"/>
+      <c r="H22" s="20" t="n"/>
+      <c r="I22" s="21">
+        <f>IF(G22="","",LEN(G22))</f>
+        <v/>
+      </c>
+      <c r="J22" s="20" t="n"/>
+      <c r="K22" s="20" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="n"/>
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="20" t="n"/>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
+      <c r="G23" s="20" t="n"/>
+      <c r="H23" s="20" t="n"/>
+      <c r="I23" s="21">
+        <f>IF(G23="","",LEN(G23))</f>
+        <v/>
+      </c>
+      <c r="J23" s="20" t="n"/>
+      <c r="K23" s="20" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="n"/>
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="20" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
+      <c r="G24" s="20" t="n"/>
+      <c r="H24" s="20" t="n"/>
+      <c r="I24" s="21">
+        <f>IF(G24="","",LEN(G24))</f>
+        <v/>
+      </c>
+      <c r="J24" s="20" t="n"/>
+      <c r="K24" s="20" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K24"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Keep current illustration,Replace with new image"</formula1>
+    <dataValidation sqref="H3 H4 H5 H6 H8 H9 H10 H12 H13 H14 H16 H17 H18 H20 H21 H22 H23 H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Keep as is,Replace with new content,Remove,Approve current text"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7181,17 +10190,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
           <t>#</t>
@@ -7199,264 +10212,243 @@
       </c>
       <c r="B1" s="13" t="inlineStr">
         <is>
-          <t>Question</t>
+          <t>Show on site? (Yes/No)</t>
         </is>
       </c>
       <c r="C1" s="13" t="inlineStr">
         <is>
-          <t>What we know so far</t>
+          <t>Client name (as approved)</t>
         </is>
       </c>
       <c r="D1" s="13" t="inlineStr">
         <is>
-          <t>Your answer</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="E1" s="13" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Website URL</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Logo file name</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Permission to show name and logo (Yes/No)</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>Show in home logo strip? (Yes/No)</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Notes for Claude</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>What does DigitizWork do? List the services you want on the site (rough bullet points are fine).</t>
-        </is>
-      </c>
-      <c r="C2" s="22" t="inlineStr">
-        <is>
-          <t>Message: 'DigitizWork can deliver any software solution using AI'. Service list on the site is a proposal.</t>
-        </is>
-      </c>
+      <c r="A2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="n"/>
+      <c r="C2" s="20" t="n"/>
       <c r="D2" s="20" t="n"/>
       <c r="E2" s="20" t="n"/>
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="20" t="n"/>
+      <c r="H2" s="20" t="n"/>
+      <c r="I2" s="20" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>Who are your customers? Business type and size, industries, B2B or B2C.</t>
-        </is>
-      </c>
-      <c r="C3" s="22" t="inlineStr"/>
+      <c r="A3" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
       <c r="D3" s="20" t="n"/>
       <c r="E3" s="20" t="n"/>
+      <c r="F3" s="20" t="n"/>
+      <c r="G3" s="20" t="n"/>
+      <c r="H3" s="20" t="n"/>
+      <c r="I3" s="20" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>Where do you operate and which markets do you serve? Language and spelling (Australian English?).</t>
-        </is>
-      </c>
-      <c r="C4" s="22" t="inlineStr">
-        <is>
-          <t>Based in Melbourne, Australia (confirmed). Markets and spelling not confirmed.</t>
-        </is>
-      </c>
+      <c r="A4" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="20" t="n"/>
+      <c r="C4" s="20" t="n"/>
       <c r="D4" s="20" t="n"/>
       <c r="E4" s="20" t="n"/>
+      <c r="F4" s="20" t="n"/>
+      <c r="G4" s="20" t="n"/>
+      <c r="H4" s="20" t="n"/>
+      <c r="I4" s="20" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>Main goal of the site? (enquiries, consultation bookings, recruiting, credibility). Which single action matters most?</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>Assumed: enquiries via the contact form.</t>
-        </is>
-      </c>
+      <c r="A5" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="20" t="n"/>
+      <c r="C5" s="20" t="n"/>
       <c r="D5" s="20" t="n"/>
       <c r="E5" s="20" t="n"/>
+      <c r="F5" s="20" t="n"/>
+      <c r="G5" s="20" t="n"/>
+      <c r="H5" s="20" t="n"/>
+      <c r="I5" s="20" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>Contact details to publish, and which inbox receives form messages?</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>Email consultant@digitizwork.com and Melbourne, Australia (confirmed). Phone, address and form inbox open.</t>
-        </is>
-      </c>
+      <c r="A6" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="20" t="n"/>
+      <c r="C6" s="20" t="n"/>
       <c r="D6" s="20" t="n"/>
       <c r="E6" s="20" t="n"/>
+      <c r="F6" s="20" t="n"/>
+      <c r="G6" s="20" t="n"/>
+      <c r="H6" s="20" t="n"/>
+      <c r="I6" s="20" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Brand assets: logo, colours, fonts? (send files if you have them)</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>None received; the current look is a proposal.</t>
-        </is>
-      </c>
+      <c r="A7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="20" t="n"/>
+      <c r="C7" s="20" t="n"/>
       <c r="D7" s="20" t="n"/>
       <c r="E7" s="20" t="n"/>
+      <c r="F7" s="20" t="n"/>
+      <c r="G7" s="20" t="n"/>
+      <c r="H7" s="20" t="n"/>
+      <c r="I7" s="20" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
-        <is>
-          <t>Q7</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>Domain and hosting: do you own a domain? Hosting preference or budget?</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr"/>
+      <c r="A8" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="20" t="n"/>
+      <c r="C8" s="20" t="n"/>
       <c r="D8" s="20" t="n"/>
       <c r="E8" s="20" t="n"/>
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20" t="n"/>
+      <c r="I8" s="20" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>Facts you can confirm: founding year, team size, founder names, legal entity name, ABN.</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr"/>
+      <c r="A9" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="20" t="n"/>
+      <c r="C9" s="20" t="n"/>
       <c r="D9" s="20" t="n"/>
       <c r="E9" s="20" t="n"/>
+      <c r="F9" s="20" t="n"/>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="20" t="n"/>
+      <c r="I9" s="20" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
-        <is>
-          <t>Q9</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>Competitor sites or sites you admire (2-5 links), and anything you dislike.</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr"/>
+      <c r="A10" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="20" t="n"/>
+      <c r="C10" s="20" t="n"/>
       <c r="D10" s="20" t="n"/>
       <c r="E10" s="20" t="n"/>
+      <c r="F10" s="20" t="n"/>
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="20" t="n"/>
+      <c r="I10" s="20" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="inlineStr">
-        <is>
-          <t>Q10</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>Privacy: confirm Australian Privacy Act applies. Cookie consent / analytics needed?</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>Assumed: Australian Privacy Act; no cookies at launch.</t>
-        </is>
-      </c>
+      <c r="A11" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="20" t="n"/>
+      <c r="C11" s="20" t="n"/>
       <c r="D11" s="20" t="n"/>
       <c r="E11" s="20" t="n"/>
+      <c r="F11" s="20" t="n"/>
+      <c r="G11" s="20" t="n"/>
+      <c r="H11" s="20" t="n"/>
+      <c r="I11" s="20" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
-        <is>
-          <t>Q11</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Analytics: OK to use privacy-friendly cookieless analytics, or none at launch?</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr"/>
+      <c r="A12" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
       <c r="D12" s="20" t="n"/>
       <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
+      <c r="I12" s="20" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="inlineStr">
-        <is>
-          <t>OQ-3</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>Privacy notice: a small /privacy page (recommended) or a section on the page?</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr"/>
+      <c r="A13" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="20" t="n"/>
+      <c r="C13" s="20" t="n"/>
       <c r="D13" s="20" t="n"/>
       <c r="E13" s="20" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="25" t="inlineStr">
-        <is>
-          <t>OQ-5</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>Keep the 'How we work' section? (see Home page tab, approach.enabled)</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>Currently shown.</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="20" t="n"/>
+      <c r="F13" s="20" t="n"/>
+      <c r="G13" s="20" t="n"/>
+      <c r="H13" s="20" t="n"/>
+      <c r="I13" s="20" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="inlineStr">
-        <is>
-          <t>OQ-8</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>Does 'launch' mean a local production build only, or a public website after testing?</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr"/>
-      <c r="D15" s="20" t="n"/>
-      <c r="E15" s="20" t="n"/>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Current:</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>The site shows 6 placeholder client cards. Field IDs: clients[n].name, clients[n].industry, clients[n].website, clients[n].logo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Logos:</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>SVG preferred, otherwise PNG/WebP with a transparent background, about 240 x 96 px. Send the files with this sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Permission:</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Only list clients who have agreed in writing to be named. Rows without 'Yes' are not shown.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2 B3 B4 B5 B6 B7 B8 B9 B10 B11 B12 B13 G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 H2 H3 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7467,137 +10459,504 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="26" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" s="26" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="C1" s="26" t="inlineStr">
-        <is>
-          <t>Changed by</t>
-        </is>
-      </c>
-      <c r="D1" s="26" t="inlineStr">
-        <is>
-          <t>Summary of changes</t>
-        </is>
-      </c>
-      <c r="E1" s="26" t="inlineStr">
-        <is>
-          <t>Jira issue (filled by Claude)</t>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>Show on site? (Yes/No)</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>Client name</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>Project title</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Challenge (1-2 sentences)</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Solution (1-2 sentences)</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Outcome (1-2 sentences)</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>Image file name (optional)</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Client approved this text (Yes/No)</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>Notes for Claude</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-      <c r="C2" s="17" t="inlineStr">
-        <is>
-          <t>Claude</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="inlineStr">
-        <is>
-          <t>Initial export of current site content (placeholder and draft copy, confirmed email and location).</t>
-        </is>
-      </c>
-      <c r="E2" s="17" t="inlineStr"/>
+      <c r="A2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="n"/>
+      <c r="C2" s="20" t="n"/>
+      <c r="D2" s="20" t="n"/>
+      <c r="E2" s="20" t="n"/>
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="20" t="n"/>
+      <c r="H2" s="20" t="n"/>
+      <c r="I2" s="20" t="n"/>
+      <c r="J2" s="20" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="n"/>
+      <c r="A3" s="17" t="n">
+        <v>2</v>
+      </c>
       <c r="B3" s="20" t="n"/>
       <c r="C3" s="20" t="n"/>
       <c r="D3" s="20" t="n"/>
-      <c r="E3" s="17" t="n"/>
+      <c r="E3" s="20" t="n"/>
+      <c r="F3" s="20" t="n"/>
+      <c r="G3" s="20" t="n"/>
+      <c r="H3" s="20" t="n"/>
+      <c r="I3" s="20" t="n"/>
+      <c r="J3" s="20" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="n"/>
+      <c r="A4" s="17" t="n">
+        <v>3</v>
+      </c>
       <c r="B4" s="20" t="n"/>
       <c r="C4" s="20" t="n"/>
       <c r="D4" s="20" t="n"/>
-      <c r="E4" s="17" t="n"/>
+      <c r="E4" s="20" t="n"/>
+      <c r="F4" s="20" t="n"/>
+      <c r="G4" s="20" t="n"/>
+      <c r="H4" s="20" t="n"/>
+      <c r="I4" s="20" t="n"/>
+      <c r="J4" s="20" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="n"/>
+      <c r="A5" s="17" t="n">
+        <v>4</v>
+      </c>
       <c r="B5" s="20" t="n"/>
       <c r="C5" s="20" t="n"/>
       <c r="D5" s="20" t="n"/>
-      <c r="E5" s="17" t="n"/>
+      <c r="E5" s="20" t="n"/>
+      <c r="F5" s="20" t="n"/>
+      <c r="G5" s="20" t="n"/>
+      <c r="H5" s="20" t="n"/>
+      <c r="I5" s="20" t="n"/>
+      <c r="J5" s="20" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n"/>
+      <c r="A6" s="17" t="n">
+        <v>5</v>
+      </c>
       <c r="B6" s="20" t="n"/>
       <c r="C6" s="20" t="n"/>
       <c r="D6" s="20" t="n"/>
-      <c r="E6" s="17" t="n"/>
+      <c r="E6" s="20" t="n"/>
+      <c r="F6" s="20" t="n"/>
+      <c r="G6" s="20" t="n"/>
+      <c r="H6" s="20" t="n"/>
+      <c r="I6" s="20" t="n"/>
+      <c r="J6" s="20" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="n"/>
+      <c r="A7" s="17" t="n">
+        <v>6</v>
+      </c>
       <c r="B7" s="20" t="n"/>
       <c r="C7" s="20" t="n"/>
       <c r="D7" s="20" t="n"/>
-      <c r="E7" s="17" t="n"/>
+      <c r="E7" s="20" t="n"/>
+      <c r="F7" s="20" t="n"/>
+      <c r="G7" s="20" t="n"/>
+      <c r="H7" s="20" t="n"/>
+      <c r="I7" s="20" t="n"/>
+      <c r="J7" s="20" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Current:</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>The site shows 2 placeholder case studies. Field IDs: caseStudies[n].client, .title, .challenge, .solution, .outcome, .image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Numbers:</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Only include figures (e.g. '40% faster') if the client has verified them in writing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Optional:</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Leave this tab empty to hide the case studies section.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2 B3 B4 B5 B6 B7 I2 I3 I4 I5 I6 I7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>Show on site? (Yes/No)</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>Quote (exact approved words)</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>Person's name</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Star rating 1-5 (optional, only if they gave it)</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>Photo file name (optional)</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Written consent to publish (Yes/No)</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>Quote characters</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>Notes for Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="n"/>
+      <c r="C2" s="20" t="n"/>
+      <c r="D2" s="20" t="n"/>
+      <c r="E2" s="20" t="n"/>
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="20" t="n"/>
+      <c r="H2" s="20" t="n"/>
+      <c r="I2" s="20" t="n"/>
+      <c r="J2" s="21">
+        <f>IF(C2="","",LEN(C2))</f>
+        <v/>
+      </c>
+      <c r="K2" s="20" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="20" t="n"/>
+      <c r="E3" s="20" t="n"/>
+      <c r="F3" s="20" t="n"/>
+      <c r="G3" s="20" t="n"/>
+      <c r="H3" s="20" t="n"/>
+      <c r="I3" s="20" t="n"/>
+      <c r="J3" s="21">
+        <f>IF(C3="","",LEN(C3))</f>
+        <v/>
+      </c>
+      <c r="K3" s="20" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="20" t="n"/>
+      <c r="C4" s="20" t="n"/>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="20" t="n"/>
+      <c r="F4" s="20" t="n"/>
+      <c r="G4" s="20" t="n"/>
+      <c r="H4" s="20" t="n"/>
+      <c r="I4" s="20" t="n"/>
+      <c r="J4" s="21">
+        <f>IF(C4="","",LEN(C4))</f>
+        <v/>
+      </c>
+      <c r="K4" s="20" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="20" t="n"/>
+      <c r="C5" s="20" t="n"/>
+      <c r="D5" s="20" t="n"/>
+      <c r="E5" s="20" t="n"/>
+      <c r="F5" s="20" t="n"/>
+      <c r="G5" s="20" t="n"/>
+      <c r="H5" s="20" t="n"/>
+      <c r="I5" s="20" t="n"/>
+      <c r="J5" s="21">
+        <f>IF(C5="","",LEN(C5))</f>
+        <v/>
+      </c>
+      <c r="K5" s="20" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="20" t="n"/>
+      <c r="C6" s="20" t="n"/>
+      <c r="D6" s="20" t="n"/>
+      <c r="E6" s="20" t="n"/>
+      <c r="F6" s="20" t="n"/>
+      <c r="G6" s="20" t="n"/>
+      <c r="H6" s="20" t="n"/>
+      <c r="I6" s="20" t="n"/>
+      <c r="J6" s="21">
+        <f>IF(C6="","",LEN(C6))</f>
+        <v/>
+      </c>
+      <c r="K6" s="20" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="20" t="n"/>
+      <c r="C7" s="20" t="n"/>
+      <c r="D7" s="20" t="n"/>
+      <c r="E7" s="20" t="n"/>
+      <c r="F7" s="20" t="n"/>
+      <c r="G7" s="20" t="n"/>
+      <c r="H7" s="20" t="n"/>
+      <c r="I7" s="20" t="n"/>
+      <c r="J7" s="21">
+        <f>IF(C7="","",LEN(C7))</f>
+        <v/>
+      </c>
+      <c r="K7" s="20" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n"/>
+      <c r="A8" s="17" t="n">
+        <v>7</v>
+      </c>
       <c r="B8" s="20" t="n"/>
       <c r="C8" s="20" t="n"/>
       <c r="D8" s="20" t="n"/>
-      <c r="E8" s="17" t="n"/>
+      <c r="E8" s="20" t="n"/>
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20" t="n"/>
+      <c r="I8" s="20" t="n"/>
+      <c r="J8" s="21">
+        <f>IF(C8="","",LEN(C8))</f>
+        <v/>
+      </c>
+      <c r="K8" s="20" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="n"/>
+      <c r="A9" s="17" t="n">
+        <v>8</v>
+      </c>
       <c r="B9" s="20" t="n"/>
       <c r="C9" s="20" t="n"/>
       <c r="D9" s="20" t="n"/>
-      <c r="E9" s="17" t="n"/>
+      <c r="E9" s="20" t="n"/>
+      <c r="F9" s="20" t="n"/>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="20" t="n"/>
+      <c r="I9" s="20" t="n"/>
+      <c r="J9" s="21">
+        <f>IF(C9="","",LEN(C9))</f>
+        <v/>
+      </c>
+      <c r="K9" s="20" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n"/>
+      <c r="A10" s="17" t="n">
+        <v>9</v>
+      </c>
       <c r="B10" s="20" t="n"/>
       <c r="C10" s="20" t="n"/>
       <c r="D10" s="20" t="n"/>
-      <c r="E10" s="17" t="n"/>
+      <c r="E10" s="20" t="n"/>
+      <c r="F10" s="20" t="n"/>
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="20" t="n"/>
+      <c r="I10" s="20" t="n"/>
+      <c r="J10" s="21">
+        <f>IF(C10="","",LEN(C10))</f>
+        <v/>
+      </c>
+      <c r="K10" s="20" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="n"/>
+      <c r="A11" s="17" t="n">
+        <v>10</v>
+      </c>
       <c r="B11" s="20" t="n"/>
       <c r="C11" s="20" t="n"/>
       <c r="D11" s="20" t="n"/>
-      <c r="E11" s="17" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="n"/>
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="17" t="n"/>
+      <c r="E11" s="20" t="n"/>
+      <c r="F11" s="20" t="n"/>
+      <c r="G11" s="20" t="n"/>
+      <c r="H11" s="20" t="n"/>
+      <c r="I11" s="20" t="n"/>
+      <c r="J11" s="21">
+        <f>IF(C11="","",LEN(C11))</f>
+        <v/>
+      </c>
+      <c r="K11" s="20" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Current:</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>The site shows 3 placeholder testimonials. Field IDs: testimonials[n].quote, .name, .role, .company, .rating, .photo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Consent:</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Australian Consumer Law prohibits fake or misleading reviews. Only real quotes, with written consent. Rows without 'Yes' are not shown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Featured:</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Testimonial #1 is also shown on the home page.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2 B3 B4 B5 B6 B7 B8 B9 B10 B11 I2 I3 I4 I5 I6 I7 I8 I9 I10 I11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>